--- a/阵营/攻防监控.xlsx
+++ b/阵营/攻防监控.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据总控" sheetId="2" r:id="rId1"/>
@@ -6886,7 +6886,7 @@
     <t>阵营攻防·拍卖掉落</t>
   </si>
   <si>
-    <t>{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},</t>
+    <t>{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="拍卖分红",},</t>
   </si>
   <si>
     <t>{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},</t>
@@ -7189,7 +7189,7 @@
     <t>据点攻防·拍卖掉落</t>
   </si>
   <si>
-    <t>{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},</t>
+    <t>{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="拍卖分红",},</t>
   </si>
   <si>
     <t>本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，险胜！浩气盟士气大涨500分！\n</t>
@@ -7763,13 +7763,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8400,28 +8394,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -8430,49 +8427,46 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -8484,7 +8478,7 @@
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -8496,7 +8490,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -8508,7 +8502,7 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -8520,7 +8514,7 @@
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -8532,7 +8526,7 @@
     <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -8544,7 +8538,7 @@
     <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -8585,13 +8579,13 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -8600,13 +8594,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="23" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="3" xfId="23" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -8660,16 +8654,16 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="22" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="22" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
@@ -8690,7 +8684,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -8702,7 +8696,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -9111,7 +9105,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="37" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1786710144000,</v>
+        <v>nTimeStamp = 1786801797000,</v>
       </c>
       <c r="B4" s="41" t="s">
         <v>11</v>
@@ -38444,7 +38438,7 @@
       </c>
       <c r="T8" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=20,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=20,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=20,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=20,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=20,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=20,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=20,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=20,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=20,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
+        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="拍卖分红",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=20,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=20,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=20,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=20,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=20,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=20,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=20,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=20,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=20,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="U8" t="s">
         <v>2275</v>
@@ -39192,7 +39186,7 @@
       </c>
       <c r="T41" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
+        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U41" t="s">
         <v>2275</v>
@@ -39211,7 +39205,7 @@
       </c>
       <c r="T42" t="str">
         <f t="shared" si="1"/>
-        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
+        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U42" t="s">
         <v>2376</v>
@@ -39728,7 +39722,7 @@
       </c>
       <c r="T68" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
+        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U68" t="s">
         <v>2275</v>
@@ -39747,7 +39741,7 @@
       </c>
       <c r="T69" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=20,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=20,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=20,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=20,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=20,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=20,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=20,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=20,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=20,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
+        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="拍卖分红",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=20,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=20,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=20,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=20,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=20,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=20,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=20,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=20,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=20,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="U69" t="s">
         <v>2376</v>
@@ -40194,7 +40188,7 @@
       </c>
       <c r="T91" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
+        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U91" t="s">
         <v>2275</v>
@@ -40213,7 +40207,7 @@
       </c>
       <c r="T92" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
+        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U92" t="s">
         <v>2376</v>
@@ -40391,7 +40385,7 @@
       </c>
       <c r="T101" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
+        <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U101" t="s">
         <v>2275</v>
@@ -40410,7 +40404,7 @@
       </c>
       <c r="T102" t="str">
         <f t="shared" si="3"/>
-        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="阵营活动",},},},</v>
+        <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U102" t="s">
         <v>2376</v>
@@ -41214,7 +41208,7 @@
         <v>1</v>
       </c>
       <c r="T131" t="str">
-        <f t="shared" ref="T131:T168" si="4">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(C131),ISBLANK(L131),ISBLANK(M131),OR(ISBLANK(B130)=FALSE,ISBLANK(C130)=FALSE,ISBLANK(L130)=FALSE,ISBLANK(M130)=FALSE)),"},},}",IF(ISBLANK(C131),"","{szContent="""&amp;C131&amp;""","&amp;IF(D131&lt;&gt;"","szNote="""&amp;D131&amp;""",","")&amp;IF(K131&lt;&gt;"","col={"&amp;K131&amp;"},","")&amp;IF(L131&gt;0,"bSearch=true,","")&amp;IF(M131&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N131&gt;0,"szVoice="""&amp;N131&amp;""",","")&amp;IF(O131&gt;0,"bTeamChannel=true,","")&amp;IF(P131&gt;0,"bWhisperChannel=true,","")&amp;IF(Q131&gt;0,"bCenterAlarm=true,","")&amp;IF(R131&gt;0,"bScreenHead=true,","")&amp;IF(S131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U131:AAF131)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="T131:T162" si="4">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(C131),ISBLANK(L131),ISBLANK(M131),OR(ISBLANK(B130)=FALSE,ISBLANK(C130)=FALSE,ISBLANK(L130)=FALSE,ISBLANK(M130)=FALSE)),"},},}",IF(ISBLANK(C131),"","{szContent="""&amp;C131&amp;""","&amp;IF(D131&lt;&gt;"","szNote="""&amp;D131&amp;""",","")&amp;IF(K131&lt;&gt;"","col={"&amp;K131&amp;"},","")&amp;IF(L131&gt;0,"bSearch=true,","")&amp;IF(M131&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N131&gt;0,"szVoice="""&amp;N131&amp;""",","")&amp;IF(O131&gt;0,"bTeamChannel=true,","")&amp;IF(P131&gt;0,"bWhisperChannel=true,","")&amp;IF(Q131&gt;0,"bCenterAlarm=true,","")&amp;IF(R131&gt;0,"bScreenHead=true,","")&amp;IF(S131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U131:AAF131)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【红莲岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【秋雨堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【红莲岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【秋雨堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·恶人大旗",},},},</v>
       </c>
       <c r="U131" t="s">
@@ -42506,7 +42500,7 @@
         <v>1</v>
       </c>
       <c r="T163" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B163)=FALSE,IF(ISBLANK(B162),"},["&amp;B163&amp;"]={","["&amp;B163&amp;"]={"),IF(AND(ISBLANK(B163),ISBLANK(C163),ISBLANK(L163),ISBLANK(M163),OR(ISBLANK(B162)=FALSE,ISBLANK(C162)=FALSE,ISBLANK(L162)=FALSE,ISBLANK(M162)=FALSE)),"},},}",IF(ISBLANK(C163),"","{szContent="""&amp;C163&amp;""","&amp;IF(D163&lt;&gt;"","szNote="""&amp;D163&amp;""",","")&amp;IF(K163&lt;&gt;"","col={"&amp;K163&amp;"},","")&amp;IF(L163&gt;0,"bSearch=true,","")&amp;IF(M163&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N163&gt;0,"szVoice="""&amp;N163&amp;""",","")&amp;IF(O163&gt;0,"bTeamChannel=true,","")&amp;IF(P163&gt;0,"bWhisperChannel=true,","")&amp;IF(Q163&gt;0,"bCenterAlarm=true,","")&amp;IF(R163&gt;0,"bScreenHead=true,","")&amp;IF(S163&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U163&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U163:AAF163)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U163" t="s">
@@ -42533,7 +42527,7 @@
         <v>656</v>
       </c>
       <c r="T164" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B164)=FALSE,IF(ISBLANK(B163),"},["&amp;B164&amp;"]={","["&amp;B164&amp;"]={"),IF(AND(ISBLANK(B164),ISBLANK(C164),ISBLANK(L164),ISBLANK(M164),OR(ISBLANK(B163)=FALSE,ISBLANK(C163)=FALSE,ISBLANK(L163)=FALSE,ISBLANK(M163)=FALSE)),"},},}",IF(ISBLANK(C164),"","{szContent="""&amp;C164&amp;""","&amp;IF(D164&lt;&gt;"","szNote="""&amp;D164&amp;""",","")&amp;IF(K164&lt;&gt;"","col={"&amp;K164&amp;"},","")&amp;IF(L164&gt;0,"bSearch=true,","")&amp;IF(M164&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N164&gt;0,"szVoice="""&amp;N164&amp;""",","")&amp;IF(O164&gt;0,"bTeamChannel=true,","")&amp;IF(P164&gt;0,"bWhisperChannel=true,","")&amp;IF(Q164&gt;0,"bCenterAlarm=true,","")&amp;IF(R164&gt;0,"bScreenHead=true,","")&amp;IF(S164&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U164&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U164:AAF164)&amp;"},","")&amp;"},")))</f>
         <v>},[656]={</v>
       </c>
     </row>
@@ -42557,7 +42551,7 @@
         <v>1</v>
       </c>
       <c r="T165" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B165)=FALSE,IF(ISBLANK(B164),"},["&amp;B165&amp;"]={","["&amp;B165&amp;"]={"),IF(AND(ISBLANK(B165),ISBLANK(C165),ISBLANK(L165),ISBLANK(M165),OR(ISBLANK(B164)=FALSE,ISBLANK(C164)=FALSE,ISBLANK(L164)=FALSE,ISBLANK(M164)=FALSE)),"},},}",IF(ISBLANK(C165),"","{szContent="""&amp;C165&amp;""","&amp;IF(D165&lt;&gt;"","szNote="""&amp;D165&amp;""",","")&amp;IF(K165&lt;&gt;"","col={"&amp;K165&amp;"},","")&amp;IF(L165&gt;0,"bSearch=true,","")&amp;IF(M165&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N165&gt;0,"szVoice="""&amp;N165&amp;""",","")&amp;IF(O165&gt;0,"bTeamChannel=true,","")&amp;IF(P165&gt;0,"bWhisperChannel=true,","")&amp;IF(Q165&gt;0,"bCenterAlarm=true,","")&amp;IF(R165&gt;0,"bScreenHead=true,","")&amp;IF(S165&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U165&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U165:AAF165)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U165" t="s">
@@ -42593,7 +42587,7 @@
         <v>1</v>
       </c>
       <c r="T166" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B166)=FALSE,IF(ISBLANK(B165),"},["&amp;B166&amp;"]={","["&amp;B166&amp;"]={"),IF(AND(ISBLANK(B166),ISBLANK(C166),ISBLANK(L166),ISBLANK(M166),OR(ISBLANK(B165)=FALSE,ISBLANK(C165)=FALSE,ISBLANK(L165)=FALSE,ISBLANK(M165)=FALSE)),"},},}",IF(ISBLANK(C166),"","{szContent="""&amp;C166&amp;""","&amp;IF(D166&lt;&gt;"","szNote="""&amp;D166&amp;""",","")&amp;IF(K166&lt;&gt;"","col={"&amp;K166&amp;"},","")&amp;IF(L166&gt;0,"bSearch=true,","")&amp;IF(M166&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N166&gt;0,"szVoice="""&amp;N166&amp;""",","")&amp;IF(O166&gt;0,"bTeamChannel=true,","")&amp;IF(P166&gt;0,"bWhisperChannel=true,","")&amp;IF(Q166&gt;0,"bCenterAlarm=true,","")&amp;IF(R166&gt;0,"bScreenHead=true,","")&amp;IF(S166&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U166&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U166:AAF166)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime="180,【云台营】大旗重置;185,【云台营】大旗重置·结束",nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime="180,【高阳营】大旗重置;185,【高阳营】大旗重置·结束",nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U166" t="s">
@@ -42629,7 +42623,7 @@
         <v>1</v>
       </c>
       <c r="T167" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B167)=FALSE,IF(ISBLANK(B166),"},["&amp;B167&amp;"]={","["&amp;B167&amp;"]={"),IF(AND(ISBLANK(B167),ISBLANK(C167),ISBLANK(L167),ISBLANK(M167),OR(ISBLANK(B166)=FALSE,ISBLANK(C166)=FALSE,ISBLANK(L166)=FALSE,ISBLANK(M166)=FALSE)),"},},}",IF(ISBLANK(C167),"","{szContent="""&amp;C167&amp;""","&amp;IF(D167&lt;&gt;"","szNote="""&amp;D167&amp;""",","")&amp;IF(K167&lt;&gt;"","col={"&amp;K167&amp;"},","")&amp;IF(L167&gt;0,"bSearch=true,","")&amp;IF(M167&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N167&gt;0,"szVoice="""&amp;N167&amp;""",","")&amp;IF(O167&gt;0,"bTeamChannel=true,","")&amp;IF(P167&gt;0,"bWhisperChannel=true,","")&amp;IF(Q167&gt;0,"bCenterAlarm=true,","")&amp;IF(R167&gt;0,"bScreenHead=true,","")&amp;IF(S167&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U167&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U167:AAF167)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U167" t="s">
@@ -42650,7 +42644,7 @@
     </row>
     <row r="168" spans="1:26">
       <c r="T168" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B168)=FALSE,IF(ISBLANK(B167),"},["&amp;B168&amp;"]={","["&amp;B168&amp;"]={"),IF(AND(ISBLANK(B168),ISBLANK(C168),ISBLANK(L168),ISBLANK(M168),OR(ISBLANK(B167)=FALSE,ISBLANK(C167)=FALSE,ISBLANK(L167)=FALSE,ISBLANK(M167)=FALSE)),"},},}",IF(ISBLANK(C168),"","{szContent="""&amp;C168&amp;""","&amp;IF(D168&lt;&gt;"","szNote="""&amp;D168&amp;""",","")&amp;IF(K168&lt;&gt;"","col={"&amp;K168&amp;"},","")&amp;IF(L168&gt;0,"bSearch=true,","")&amp;IF(M168&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N168&gt;0,"szVoice="""&amp;N168&amp;""",","")&amp;IF(O168&gt;0,"bTeamChannel=true,","")&amp;IF(P168&gt;0,"bWhisperChannel=true,","")&amp;IF(Q168&gt;0,"bCenterAlarm=true,","")&amp;IF(R168&gt;0,"bScreenHead=true,","")&amp;IF(S168&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U168&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U168:AAF168)&amp;"},","")&amp;"},")))</f>
         <v>},},}</v>
       </c>
     </row>

--- a/阵营/攻防监控.xlsx
+++ b/阵营/攻防监控.xlsx
@@ -7318,7 +7318,7 @@
     <t>本场贡献值进入前1200名，额外获得3000威名，可通过邮件领取\n</t>
   </si>
   <si>
-    <t>{nClass=20,nIcon=3536,nFrame=6,szName="攻防进入前1200名",nTime=10,key="阵营活动",},</t>
+    <t>据点攻防·进入前1200名</t>
   </si>
   <si>
     <t>{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,key="{$3}·浩气大旗",},</t>
@@ -9105,7 +9105,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="37" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1786801797000,</v>
+        <v>nTimeStamp = 1787331730000,</v>
       </c>
       <c r="B4" s="41" t="s">
         <v>11</v>
@@ -39757,15 +39757,18 @@
       <c r="C70" t="s">
         <v>2418</v>
       </c>
+      <c r="D70" t="s">
+        <v>2419</v>
+      </c>
       <c r="K70" t="s">
         <v>1980</v>
       </c>
+      <c r="Q70">
+        <v>1</v>
+      </c>
       <c r="T70" t="str">
         <f t="shared" si="2"/>
-        <v>{szContent="本场贡献值进入前1200名，额外获得3000威名，可通过邮件领取\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=6,szName="攻防进入前1200名",nTime=10,key="阵营活动",},},},</v>
-      </c>
-      <c r="U70" t="s">
-        <v>2419</v>
+        <v>{szContent="本场贡献值进入前1200名，额外获得3000威名，可通过邮件领取\n",szNote="据点攻防·进入前1200名",col={255,255,100,},[20]={bCenterAlarm=true,},},</v>
       </c>
     </row>
     <row r="71" spans="1:26">

--- a/阵营/攻防监控.xlsx
+++ b/阵营/攻防监控.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="8"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据总控" sheetId="2" r:id="rId1"/>
@@ -6550,13 +6550,13 @@
     <t>{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},</t>
   </si>
   <si>
-    <t>{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},</t>
+    <t>{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},</t>
   </si>
   <si>
     <t>留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。</t>
   </si>
   <si>
-    <t>{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},</t>
+    <t>{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},</t>
   </si>
   <si>
     <t>您因消极怠战,扰乱阵营秩序，被阵营督查官请离当前地图，但同时给予250点贡献积分！</t>
@@ -9105,7 +9105,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="37" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1787331730000,</v>
+        <v>nTimeStamp = 1788193460000,</v>
       </c>
       <c r="B4" s="41" t="s">
         <v>11</v>
@@ -36681,7 +36681,7 @@
       <c r="O107"/>
       <c r="V107" t="str">
         <f t="shared" si="19"/>
-        <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
+        <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W107" t="s">
         <v>2162</v>
@@ -36707,7 +36707,7 @@
       <c r="O108"/>
       <c r="V108" t="str">
         <f t="shared" si="19"/>
-        <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
+        <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W108" t="s">
         <v>2162</v>
@@ -37737,7 +37737,7 @@
       </c>
       <c r="V153" t="str">
         <f t="shared" si="20"/>
-        <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
+        <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W153" t="s">
         <v>2162</v>
@@ -37762,7 +37762,7 @@
       </c>
       <c r="V154" t="str">
         <f t="shared" si="20"/>
-        <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
+        <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W154" t="s">
         <v>2162</v>
@@ -38069,7 +38069,7 @@
       </c>
       <c r="V166" t="str">
         <f t="shared" si="20"/>
-        <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
+        <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W166" t="s">
         <v>2162</v>
@@ -38094,7 +38094,7 @@
       </c>
       <c r="V167" t="str">
         <f t="shared" si="20"/>
-        <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=5,key="狼牙先锋首领",},},},</v>
+        <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W167" t="s">
         <v>2162</v>
@@ -41211,7 +41211,7 @@
         <v>1</v>
       </c>
       <c r="T131" t="str">
-        <f t="shared" ref="T131:T162" si="4">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(C131),ISBLANK(L131),ISBLANK(M131),OR(ISBLANK(B130)=FALSE,ISBLANK(C130)=FALSE,ISBLANK(L130)=FALSE,ISBLANK(M130)=FALSE)),"},},}",IF(ISBLANK(C131),"","{szContent="""&amp;C131&amp;""","&amp;IF(D131&lt;&gt;"","szNote="""&amp;D131&amp;""",","")&amp;IF(K131&lt;&gt;"","col={"&amp;K131&amp;"},","")&amp;IF(L131&gt;0,"bSearch=true,","")&amp;IF(M131&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N131&gt;0,"szVoice="""&amp;N131&amp;""",","")&amp;IF(O131&gt;0,"bTeamChannel=true,","")&amp;IF(P131&gt;0,"bWhisperChannel=true,","")&amp;IF(Q131&gt;0,"bCenterAlarm=true,","")&amp;IF(R131&gt;0,"bScreenHead=true,","")&amp;IF(S131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U131:AAF131)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="T131:T168" si="4">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(C131),ISBLANK(L131),ISBLANK(M131),OR(ISBLANK(B130)=FALSE,ISBLANK(C130)=FALSE,ISBLANK(L130)=FALSE,ISBLANK(M130)=FALSE)),"},},}",IF(ISBLANK(C131),"","{szContent="""&amp;C131&amp;""","&amp;IF(D131&lt;&gt;"","szNote="""&amp;D131&amp;""",","")&amp;IF(K131&lt;&gt;"","col={"&amp;K131&amp;"},","")&amp;IF(L131&gt;0,"bSearch=true,","")&amp;IF(M131&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N131&gt;0,"szVoice="""&amp;N131&amp;""",","")&amp;IF(O131&gt;0,"bTeamChannel=true,","")&amp;IF(P131&gt;0,"bWhisperChannel=true,","")&amp;IF(Q131&gt;0,"bCenterAlarm=true,","")&amp;IF(R131&gt;0,"bScreenHead=true,","")&amp;IF(S131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U131:AAF131)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【红莲岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【秋雨堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【红莲岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【秋雨堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·恶人大旗",},},},</v>
       </c>
       <c r="U131" t="s">
@@ -42503,7 +42503,7 @@
         <v>1</v>
       </c>
       <c r="T163" t="str">
-        <f>IF(ISBLANK(B163)=FALSE,IF(ISBLANK(B162),"},["&amp;B163&amp;"]={","["&amp;B163&amp;"]={"),IF(AND(ISBLANK(B163),ISBLANK(C163),ISBLANK(L163),ISBLANK(M163),OR(ISBLANK(B162)=FALSE,ISBLANK(C162)=FALSE,ISBLANK(L162)=FALSE,ISBLANK(M162)=FALSE)),"},},}",IF(ISBLANK(C163),"","{szContent="""&amp;C163&amp;""","&amp;IF(D163&lt;&gt;"","szNote="""&amp;D163&amp;""",","")&amp;IF(K163&lt;&gt;"","col={"&amp;K163&amp;"},","")&amp;IF(L163&gt;0,"bSearch=true,","")&amp;IF(M163&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N163&gt;0,"szVoice="""&amp;N163&amp;""",","")&amp;IF(O163&gt;0,"bTeamChannel=true,","")&amp;IF(P163&gt;0,"bWhisperChannel=true,","")&amp;IF(Q163&gt;0,"bCenterAlarm=true,","")&amp;IF(R163&gt;0,"bScreenHead=true,","")&amp;IF(S163&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U163&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U163:AAF163)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="4"/>
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U163" t="s">
@@ -42530,7 +42530,7 @@
         <v>656</v>
       </c>
       <c r="T164" t="str">
-        <f>IF(ISBLANK(B164)=FALSE,IF(ISBLANK(B163),"},["&amp;B164&amp;"]={","["&amp;B164&amp;"]={"),IF(AND(ISBLANK(B164),ISBLANK(C164),ISBLANK(L164),ISBLANK(M164),OR(ISBLANK(B163)=FALSE,ISBLANK(C163)=FALSE,ISBLANK(L163)=FALSE,ISBLANK(M163)=FALSE)),"},},}",IF(ISBLANK(C164),"","{szContent="""&amp;C164&amp;""","&amp;IF(D164&lt;&gt;"","szNote="""&amp;D164&amp;""",","")&amp;IF(K164&lt;&gt;"","col={"&amp;K164&amp;"},","")&amp;IF(L164&gt;0,"bSearch=true,","")&amp;IF(M164&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N164&gt;0,"szVoice="""&amp;N164&amp;""",","")&amp;IF(O164&gt;0,"bTeamChannel=true,","")&amp;IF(P164&gt;0,"bWhisperChannel=true,","")&amp;IF(Q164&gt;0,"bCenterAlarm=true,","")&amp;IF(R164&gt;0,"bScreenHead=true,","")&amp;IF(S164&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U164&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U164:AAF164)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="4"/>
         <v>},[656]={</v>
       </c>
     </row>
@@ -42554,7 +42554,7 @@
         <v>1</v>
       </c>
       <c r="T165" t="str">
-        <f>IF(ISBLANK(B165)=FALSE,IF(ISBLANK(B164),"},["&amp;B165&amp;"]={","["&amp;B165&amp;"]={"),IF(AND(ISBLANK(B165),ISBLANK(C165),ISBLANK(L165),ISBLANK(M165),OR(ISBLANK(B164)=FALSE,ISBLANK(C164)=FALSE,ISBLANK(L164)=FALSE,ISBLANK(M164)=FALSE)),"},},}",IF(ISBLANK(C165),"","{szContent="""&amp;C165&amp;""","&amp;IF(D165&lt;&gt;"","szNote="""&amp;D165&amp;""",","")&amp;IF(K165&lt;&gt;"","col={"&amp;K165&amp;"},","")&amp;IF(L165&gt;0,"bSearch=true,","")&amp;IF(M165&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N165&gt;0,"szVoice="""&amp;N165&amp;""",","")&amp;IF(O165&gt;0,"bTeamChannel=true,","")&amp;IF(P165&gt;0,"bWhisperChannel=true,","")&amp;IF(Q165&gt;0,"bCenterAlarm=true,","")&amp;IF(R165&gt;0,"bScreenHead=true,","")&amp;IF(S165&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U165&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U165:AAF165)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="4"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U165" t="s">
@@ -42590,7 +42590,7 @@
         <v>1</v>
       </c>
       <c r="T166" t="str">
-        <f>IF(ISBLANK(B166)=FALSE,IF(ISBLANK(B165),"},["&amp;B166&amp;"]={","["&amp;B166&amp;"]={"),IF(AND(ISBLANK(B166),ISBLANK(C166),ISBLANK(L166),ISBLANK(M166),OR(ISBLANK(B165)=FALSE,ISBLANK(C165)=FALSE,ISBLANK(L165)=FALSE,ISBLANK(M165)=FALSE)),"},},}",IF(ISBLANK(C166),"","{szContent="""&amp;C166&amp;""","&amp;IF(D166&lt;&gt;"","szNote="""&amp;D166&amp;""",","")&amp;IF(K166&lt;&gt;"","col={"&amp;K166&amp;"},","")&amp;IF(L166&gt;0,"bSearch=true,","")&amp;IF(M166&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N166&gt;0,"szVoice="""&amp;N166&amp;""",","")&amp;IF(O166&gt;0,"bTeamChannel=true,","")&amp;IF(P166&gt;0,"bWhisperChannel=true,","")&amp;IF(Q166&gt;0,"bCenterAlarm=true,","")&amp;IF(R166&gt;0,"bScreenHead=true,","")&amp;IF(S166&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U166&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U166:AAF166)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="4"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime="180,【云台营】大旗重置;185,【云台营】大旗重置·结束",nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime="180,【高阳营】大旗重置;185,【高阳营】大旗重置·结束",nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U166" t="s">
@@ -42626,7 +42626,7 @@
         <v>1</v>
       </c>
       <c r="T167" t="str">
-        <f>IF(ISBLANK(B167)=FALSE,IF(ISBLANK(B166),"},["&amp;B167&amp;"]={","["&amp;B167&amp;"]={"),IF(AND(ISBLANK(B167),ISBLANK(C167),ISBLANK(L167),ISBLANK(M167),OR(ISBLANK(B166)=FALSE,ISBLANK(C166)=FALSE,ISBLANK(L166)=FALSE,ISBLANK(M166)=FALSE)),"},},}",IF(ISBLANK(C167),"","{szContent="""&amp;C167&amp;""","&amp;IF(D167&lt;&gt;"","szNote="""&amp;D167&amp;""",","")&amp;IF(K167&lt;&gt;"","col={"&amp;K167&amp;"},","")&amp;IF(L167&gt;0,"bSearch=true,","")&amp;IF(M167&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N167&gt;0,"szVoice="""&amp;N167&amp;""",","")&amp;IF(O167&gt;0,"bTeamChannel=true,","")&amp;IF(P167&gt;0,"bWhisperChannel=true,","")&amp;IF(Q167&gt;0,"bCenterAlarm=true,","")&amp;IF(R167&gt;0,"bScreenHead=true,","")&amp;IF(S167&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U167&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U167:AAF167)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="4"/>
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U167" t="s">
@@ -42647,7 +42647,7 @@
     </row>
     <row r="168" spans="1:26">
       <c r="T168" t="str">
-        <f>IF(ISBLANK(B168)=FALSE,IF(ISBLANK(B167),"},["&amp;B168&amp;"]={","["&amp;B168&amp;"]={"),IF(AND(ISBLANK(B168),ISBLANK(C168),ISBLANK(L168),ISBLANK(M168),OR(ISBLANK(B167)=FALSE,ISBLANK(C167)=FALSE,ISBLANK(L167)=FALSE,ISBLANK(M167)=FALSE)),"},},}",IF(ISBLANK(C168),"","{szContent="""&amp;C168&amp;""","&amp;IF(D168&lt;&gt;"","szNote="""&amp;D168&amp;""",","")&amp;IF(K168&lt;&gt;"","col={"&amp;K168&amp;"},","")&amp;IF(L168&gt;0,"bSearch=true,","")&amp;IF(M168&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N168&gt;0,"szVoice="""&amp;N168&amp;""",","")&amp;IF(O168&gt;0,"bTeamChannel=true,","")&amp;IF(P168&gt;0,"bWhisperChannel=true,","")&amp;IF(Q168&gt;0,"bCenterAlarm=true,","")&amp;IF(R168&gt;0,"bScreenHead=true,","")&amp;IF(S168&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U168&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U168:AAF168)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="4"/>
         <v>},},}</v>
       </c>
     </row>

--- a/阵营/攻防监控.xlsx
+++ b/阵营/攻防监控.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据总控" sheetId="2" r:id="rId1"/>
@@ -4816,7 +4816,7 @@
     <t>神机雷</t>
   </si>
   <si>
-    <t>#FFFFFFDD</t>
+    <t>#FFFFFF00</t>
   </si>
   <si>
     <t>阵营惩罚</t>
@@ -9105,7 +9105,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="37" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1788193460000,</v>
+        <v>nTimeStamp = 1788279807000,</v>
       </c>
       <c r="B4" s="41" t="s">
         <v>11</v>
@@ -21135,11 +21135,11 @@
         <v>1585</v>
       </c>
       <c r="AI27">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=9632,nLevel=1,nScrutinyType=2,szNote="神机雷",col={255,255,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=1,col="#FFFFFFDD",nColAlpha=221,},},},</v>
+        <v>{dwID=9632,nLevel=1,nScrutinyType=2,szNote="神机雷",col={255,255,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=1,col="#FFFFFF00",},},},</v>
       </c>
     </row>
     <row r="28" customFormat="1" spans="1:46">
@@ -21996,11 +21996,11 @@
         <v>1585</v>
       </c>
       <c r="AI49">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="AN49" t="str">
         <f t="shared" si="1"/>
-        <v>{dwID=7723,nLevel=1,nScrutinyType=2,szNote="神机雷",col={255,255,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=1,col="#FFFFFFDD",nColAlpha=221,},},},</v>
+        <v>{dwID=7723,nLevel=1,nScrutinyType=2,szNote="神机雷",col={255,255,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=1,col="#FFFFFF00",},},},</v>
       </c>
     </row>
     <row r="50" spans="1:42">
@@ -22800,11 +22800,11 @@
         <v>1585</v>
       </c>
       <c r="AI68">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="AN68" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=7723,nLevel=1,nScrutinyType=2,szNote="神机雷",col={255,255,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=1,col="#FFFFFFDD",nColAlpha=221,},},},</v>
+        <v>{dwID=7723,nLevel=1,nScrutinyType=2,szNote="神机雷",col={255,255,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=1,col="#FFFFFF00",},},},</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:45">
@@ -23604,11 +23604,11 @@
         <v>1585</v>
       </c>
       <c r="AI87">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="AN87" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=7723,nLevel=1,nScrutinyType=2,szNote="神机雷",col={255,255,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=1,col="#FFFFFFDD",nColAlpha=221,},},},</v>
+        <v>{dwID=7723,nLevel=1,nScrutinyType=2,szNote="神机雷",col={255,255,255,},[1]={bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{nPriority=1,col="#FFFFFF00",},},},</v>
       </c>
     </row>
     <row r="88" spans="3:45">
